--- a/05_Figures/F07_keepers/c_data/F07_keepers_source_data.xlsx
+++ b/05_Figures/F07_keepers/c_data/F07_keepers_source_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -172,10 +172,13 @@
     <t xml:space="preserve">spls  (acute)</t>
   </si>
   <si>
-    <t xml:space="preserve">modules|svm|acute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">svm  (acute)</t>
+    <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modules|svm|total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">svm  (total)</t>
   </si>
   <si>
     <t xml:space="preserve">modules|pam|acute</t>
@@ -293,15 +296,6 @@
   </si>
   <si>
     <t xml:space="preserve">modules|spls|trajectory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modules|svm|total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">svm  (total)</t>
   </si>
   <si>
     <t xml:space="preserve">modules|rf|trajectory</t>
@@ -802,7 +796,7 @@
         <v>237</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>0.729166666666667</v>
@@ -813,14 +807,24 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
+      <c r="K2" t="n">
+        <v>0.134328358208955</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.441979166666667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.241947700012745</v>
+      </c>
       <c r="N2" t="n">
         <v>7</v>
       </c>
-      <c r="O2"/>
-      <c r="P2"/>
+      <c r="O2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.875</v>
+      </c>
       <c r="Q2" t="n">
         <v>0.5</v>
       </c>
@@ -854,7 +858,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.660714285714286</v>
@@ -865,14 +869,24 @@
       <c r="J3" t="n">
         <v>0.974409546778466</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="K3" t="n">
+        <v>0.0597014925373134</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.319107142857143</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.20099924398478</v>
+      </c>
       <c r="N3" t="n">
         <v>7</v>
       </c>
-      <c r="O3"/>
-      <c r="P3"/>
+      <c r="O3" t="n">
+        <v>0.0169642857142858</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.678571428571429</v>
+      </c>
       <c r="Q3" t="n">
         <v>0.5</v>
       </c>
@@ -897,7 +911,7 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
@@ -906,25 +920,35 @@
         <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.168318490808307</v>
+        <v>0.13069450138736</v>
       </c>
       <c r="J4" t="n">
-        <v>0.831681509191693</v>
-      </c>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
+        <v>0.762162641469783</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.348258706467662</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.335535714285714</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.254413092607442</v>
+      </c>
       <c r="N4" t="n">
         <v>7</v>
       </c>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.786607142857143</v>
+      </c>
       <c r="Q4" t="n">
         <v>0.5</v>
       </c>
@@ -958,7 +982,7 @@
         <v>237</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0.4375</v>
@@ -969,14 +993,24 @@
       <c r="J5" t="n">
         <v>0.786032211267904</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="K5" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.197395833333333</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.263224498552189</v>
+      </c>
       <c r="N5" t="n">
         <v>7</v>
       </c>
-      <c r="O5"/>
-      <c r="P5"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.751041666666666</v>
+      </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
@@ -1010,7 +1044,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0.375</v>
@@ -1021,14 +1055,24 @@
       <c r="J6" t="n">
         <v>0.692759797890566</v>
       </c>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
+      <c r="K6" t="n">
+        <v>0.144278606965174</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.100446428571429</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.219723694408278</v>
+      </c>
       <c r="N6" t="n">
         <v>7</v>
       </c>
-      <c r="O6"/>
-      <c r="P6"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.661607142857143</v>
+      </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
@@ -1062,7 +1106,7 @@
         <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
         <v>0.142857142857143</v>
@@ -1073,14 +1117,24 @@
       <c r="J7" t="n">
         <v>0.422851997791436</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
+      <c r="K7" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.105982142857143</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.225962638790841</v>
+      </c>
       <c r="N7" t="n">
         <v>7</v>
       </c>
-      <c r="O7"/>
-      <c r="P7"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.6625</v>
+      </c>
       <c r="Q7" t="n">
         <v>0.5</v>
       </c>
@@ -1114,7 +1168,7 @@
         <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1125,14 +1179,24 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0158928571428571</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.090856428083261</v>
+      </c>
       <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="O8"/>
-      <c r="P8"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0.5</v>
       </c>
@@ -1166,7 +1230,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H9" t="n">
         <v>0.732142857142857</v>
@@ -1177,14 +1241,24 @@
       <c r="J9" t="n">
         <v>0.990578946078055</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
+      <c r="K9" t="n">
+        <v>0.139303482587065</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.518883928571429</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.180024101817027</v>
+      </c>
       <c r="N9" t="n">
         <v>6</v>
       </c>
-      <c r="O9"/>
-      <c r="P9"/>
+      <c r="O9" t="n">
+        <v>0.276339285714286</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.857142857142857</v>
+      </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
@@ -1218,7 +1292,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
         <v>0.5</v>
@@ -1229,14 +1303,24 @@
       <c r="J10" t="n">
         <v>0.823490578067923</v>
       </c>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
+      <c r="K10" t="n">
+        <v>0.298507462686567</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.368303571428571</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.203488112035621</v>
+      </c>
       <c r="N10" t="n">
         <v>7</v>
       </c>
-      <c r="O10"/>
-      <c r="P10"/>
+      <c r="O10" t="n">
+        <v>0.0178571428571429</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.696428571428571</v>
+      </c>
       <c r="Q10" t="n">
         <v>0.5</v>
       </c>
@@ -1270,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
         <v>0.5</v>
@@ -1281,14 +1365,24 @@
       <c r="J11" t="n">
         <v>0.823219987825617</v>
       </c>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
+      <c r="K11" t="n">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.410089285714286</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.213726968807571</v>
+      </c>
       <c r="N11" t="n">
         <v>7</v>
       </c>
-      <c r="O11"/>
-      <c r="P11"/>
+      <c r="O11" t="n">
+        <v>0.0883928571428572</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.767857142857143</v>
+      </c>
       <c r="Q11" t="n">
         <v>0.5</v>
       </c>
@@ -1307,40 +1401,50 @@
         <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>0.482142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
-        <v>0.482142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="I12" t="n">
-        <v>0.153730967094126</v>
+        <v>0.0377204632497903</v>
       </c>
       <c r="J12" t="n">
-        <v>0.810554747191589</v>
-      </c>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
+        <v>0.71227953675021</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.296770833333333</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.25374513246453</v>
+      </c>
       <c r="N12" t="n">
         <v>7</v>
       </c>
-      <c r="O12"/>
-      <c r="P12"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.791666666666667</v>
+      </c>
       <c r="Q12" t="n">
         <v>0.5</v>
       </c>
@@ -1348,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -1374,7 +1478,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
         <v>0.196428571428571</v>
@@ -1385,14 +1489,24 @@
       <c r="J13" t="n">
         <v>0.465263732604026</v>
       </c>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
+      <c r="K13" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.138035714285714</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.181664790036149</v>
+      </c>
       <c r="N13" t="n">
         <v>7</v>
       </c>
-      <c r="O13"/>
-      <c r="P13"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.517857142857143</v>
+      </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
@@ -1400,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -1426,7 +1540,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1437,14 +1551,24 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0694642857142857</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.199209335364792</v>
+      </c>
       <c r="N14" t="n">
         <v>7</v>
       </c>
-      <c r="O14"/>
-      <c r="P14"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.661607142857143</v>
+      </c>
       <c r="Q14" t="n">
         <v>0.5</v>
       </c>
@@ -1452,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T14" t="s">
         <v>41</v>
@@ -1478,7 +1602,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1489,14 +1613,24 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0728571428571428</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.216483110032967</v>
+      </c>
       <c r="N15" t="n">
         <v>7</v>
       </c>
-      <c r="O15"/>
-      <c r="P15"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.733035714285714</v>
+      </c>
       <c r="Q15" t="n">
         <v>0.5</v>
       </c>
@@ -1504,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1530,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1541,14 +1675,24 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0238392857142857</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.112187953893319</v>
+      </c>
       <c r="N16" t="n">
         <v>7</v>
       </c>
-      <c r="O16"/>
-      <c r="P16"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.125892857142857</v>
+      </c>
       <c r="Q16" t="n">
         <v>0.5</v>
       </c>
@@ -1556,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T16" t="s">
         <v>44</v>
@@ -1564,16 +1708,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
@@ -1582,25 +1726,35 @@
         <v>1899</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H17" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.166412912013105</v>
+        <v>0.241842902721225</v>
       </c>
       <c r="J17" t="n">
-        <v>0.916920421320228</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
+        <v>0.924823763945441</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.320833333333333</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.269594350650839</v>
+      </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
-      <c r="O17"/>
-      <c r="P17"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="Q17" t="n">
         <v>0.5</v>
       </c>
@@ -1608,18 +1762,18 @@
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
@@ -1634,7 +1788,7 @@
         <v>1899</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H18" t="n">
         <v>0.535714285714286</v>
@@ -1645,14 +1799,24 @@
       <c r="J18" t="n">
         <v>0.891493263984734</v>
       </c>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
+      <c r="K18" t="n">
+        <v>0.353233830845771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.428035714285714</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.237414669534603</v>
+      </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
-      <c r="O18"/>
-      <c r="P18"/>
+      <c r="O18" t="n">
+        <v>0.0705357142857143</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.840178571428571</v>
+      </c>
       <c r="Q18" t="n">
         <v>0.5</v>
       </c>
@@ -1660,18 +1824,18 @@
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -1686,7 +1850,7 @@
         <v>1899</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
         <v>0.482142857142857</v>
@@ -1697,14 +1861,24 @@
       <c r="J19" t="n">
         <v>0.811087163466639</v>
       </c>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
+      <c r="K19" t="n">
+        <v>0.218905472636816</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.24394333708367</v>
+      </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
-      <c r="O19"/>
-      <c r="P19"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.715178571428571</v>
+      </c>
       <c r="Q19" t="n">
         <v>0.5</v>
       </c>
@@ -1712,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
@@ -1738,7 +1912,7 @@
         <v>1900</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
         <v>0.428571428571428</v>
@@ -1749,14 +1923,24 @@
       <c r="J20" t="n">
         <v>0.760780114004445</v>
       </c>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
+      <c r="K20" t="n">
+        <v>0.243781094527363</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.276964285714286</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.19340731063323</v>
+      </c>
       <c r="N20" t="n">
         <v>7</v>
       </c>
-      <c r="O20"/>
-      <c r="P20"/>
+      <c r="O20" t="n">
+        <v>0.0178571428571429</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.625892857142857</v>
+      </c>
       <c r="Q20" t="n">
         <v>0.5</v>
       </c>
@@ -1764,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T20" t="s">
         <v>28</v>
@@ -1772,7 +1956,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
@@ -1790,7 +1974,7 @@
         <v>1900</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1801,14 +1985,24 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.104196428571429</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.207776661588622</v>
+      </c>
       <c r="N21" t="n">
         <v>7</v>
       </c>
-      <c r="O21"/>
-      <c r="P21"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.679464285714286</v>
+      </c>
       <c r="Q21" t="n">
         <v>0.5</v>
       </c>
@@ -1816,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T21" t="s">
         <v>41</v>
@@ -1824,7 +2018,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -1842,7 +2036,7 @@
         <v>1900</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1853,14 +2047,24 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.113214285714286</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.213674949161307</v>
+      </c>
       <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="O22"/>
-      <c r="P22"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.591964285714284</v>
+      </c>
       <c r="Q22" t="n">
         <v>0.5</v>
       </c>
@@ -1868,15 +2072,15 @@
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
@@ -1894,7 +2098,7 @@
         <v>1900</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1905,14 +2109,24 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.00205357142857143</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0266238528978017</v>
+      </c>
       <c r="N23" t="n">
         <v>7</v>
       </c>
-      <c r="O23"/>
-      <c r="P23"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0.5</v>
       </c>
@@ -1920,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T23" t="s">
         <v>44</v>
@@ -1945,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1960,22 +2174,22 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N1" t="s">
         <v>3</v>
@@ -2019,7 +2233,7 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
         <v>30</v>
@@ -2031,7 +2245,7 @@
         <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>0.620937211013559</v>
@@ -2039,26 +2253,44 @@
       <c r="I2" t="n">
         <v>0.87004616344005</v>
       </c>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
+      <c r="J2" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.01739479271618</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.958346038400894</v>
+      </c>
       <c r="N2" t="n">
         <v>0.620937211013559</v>
       </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
+      <c r="O2" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1.01739479271618</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.958346038400894</v>
+      </c>
       <c r="R2" t="n">
         <v>42</v>
       </c>
-      <c r="S2"/>
-      <c r="T2"/>
+      <c r="S2" t="n">
+        <v>-2.99597796957357</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.213535024255417</v>
+      </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="s">
         <v>31</v>
@@ -2075,7 +2307,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -2087,7 +2319,7 @@
         <v>237</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.411266403925074</v>
@@ -2095,26 +2327,44 @@
       <c r="I3" t="n">
         <v>0.67032967032967</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0447761194029851</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.746450270442581</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.731814620750024</v>
+      </c>
       <c r="N3" t="n">
         <v>0.411266403925074</v>
       </c>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
+      <c r="O3" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.746450270442581</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.731814620750024</v>
+      </c>
       <c r="R3" t="n">
         <v>42</v>
       </c>
-      <c r="S3"/>
-      <c r="T3"/>
+      <c r="S3" t="n">
+        <v>-2.19270612623952</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.296474501089059</v>
+      </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="s">
         <v>23</v>
@@ -2131,7 +2381,7 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -2143,7 +2393,7 @@
         <v>237</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
         <v>0.259726105892755</v>
@@ -2151,32 +2401,50 @@
       <c r="I4" t="n">
         <v>0.525274725274725</v>
       </c>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
+      <c r="J4" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.186438934688261</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.138191298603544</v>
+      </c>
       <c r="N4" t="n">
         <v>0.259726105892755</v>
       </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
+      <c r="O4" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.186438934688261</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.138191298603544</v>
+      </c>
       <c r="R4" t="n">
         <v>42</v>
       </c>
-      <c r="S4"/>
-      <c r="T4"/>
+      <c r="S4" t="n">
+        <v>-0.378679567874654</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0423994795376123</v>
+      </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -2187,7 +2455,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
@@ -2199,7 +2467,7 @@
         <v>237</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0.17778999080829</v>
@@ -2207,32 +2475,50 @@
       <c r="I5" t="n">
         <v>0.446153846153846</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="J5" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.212031969926516</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.192339074737823</v>
+      </c>
       <c r="N5" t="n">
         <v>0.17778999080829</v>
       </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
+      <c r="O5" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.212031969926516</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.192339074737823</v>
+      </c>
       <c r="R5" t="n">
         <v>42</v>
       </c>
-      <c r="S5"/>
-      <c r="T5"/>
+      <c r="S5" t="n">
+        <v>-0.483899319109462</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0605621809575338</v>
+      </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -2243,7 +2529,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -2255,7 +2541,7 @@
         <v>237</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0.162702655113724</v>
@@ -2263,32 +2549,50 @@
       <c r="I6" t="n">
         <v>0.556043956043956</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
+      <c r="J6" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.192847165091876</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.136850848173076</v>
+      </c>
       <c r="N6" t="n">
         <v>0.162702655113724</v>
       </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
+      <c r="O6" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.192847165091876</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.136850848173076</v>
+      </c>
       <c r="R6" t="n">
         <v>42</v>
       </c>
-      <c r="S6"/>
-      <c r="T6"/>
+      <c r="S6" t="n">
+        <v>-0.388055651191463</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.0565154017031282</v>
+      </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -2299,7 +2603,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -2311,7 +2615,7 @@
         <v>237</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
         <v>0.077556765871716</v>
@@ -2319,32 +2623,50 @@
       <c r="I7" t="n">
         <v>0.415384615384615</v>
       </c>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
+      <c r="J7" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.157106296210139</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0457359998087378</v>
+      </c>
       <c r="N7" t="n">
         <v>0.077556765871716</v>
       </c>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7"/>
+      <c r="O7" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.157106296210139</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0457359998087378</v>
+      </c>
       <c r="R7" t="n">
         <v>42</v>
       </c>
-      <c r="S7"/>
-      <c r="T7"/>
+      <c r="S7" t="n">
+        <v>-0.193426444665325</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.119187208873766</v>
+      </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -2355,7 +2677,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -2367,7 +2689,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>0.462372213177816</v>
@@ -2375,32 +2697,50 @@
       <c r="I8" t="n">
         <v>0.778571428571428</v>
       </c>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
+      <c r="J8" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.452720615773047</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04103533694376</v>
+      </c>
       <c r="N8" t="n">
         <v>0.462372213177816</v>
       </c>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8"/>
+      <c r="O8" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.452720615773047</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.04103533694376</v>
+      </c>
       <c r="R8" t="n">
         <v>42</v>
       </c>
-      <c r="S8"/>
-      <c r="T8"/>
+      <c r="S8" t="n">
+        <v>-1.71279244365411</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.0859061716097375</v>
+      </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -2411,7 +2751,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -2423,7 +2763,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H9" t="n">
         <v>0.444504844977317</v>
@@ -2431,29 +2771,47 @@
       <c r="I9" t="n">
         <v>0.775</v>
       </c>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
+      <c r="J9" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.453419917090597</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06810987167105</v>
+      </c>
       <c r="N9" t="n">
         <v>0.444504844977317</v>
       </c>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
+      <c r="O9" t="n">
+        <v>0.0199004975124378</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.453419917090597</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.06810987167105</v>
+      </c>
       <c r="R9" t="n">
         <v>42</v>
       </c>
-      <c r="S9"/>
-      <c r="T9"/>
+      <c r="S9" t="n">
+        <v>-1.73254734585726</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.00254606388241447</v>
+      </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X9" t="s">
         <v>41</v>
@@ -2467,7 +2825,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -2479,7 +2837,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
         <v>0.400204457349602</v>
@@ -2487,29 +2845,47 @@
       <c r="I10" t="n">
         <v>0.542857142857143</v>
       </c>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
+      <c r="J10" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0447761194029851</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.631937274941917</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.667080536893519</v>
+      </c>
       <c r="N10" t="n">
         <v>0.400204457349602</v>
       </c>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
+      <c r="O10" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.631937274941917</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.667080536893519</v>
+      </c>
       <c r="R10" t="n">
         <v>42</v>
       </c>
-      <c r="S10"/>
-      <c r="T10"/>
+      <c r="S10" t="n">
+        <v>-1.73878951444609</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.194239379625306</v>
+      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X10" t="s">
         <v>24</v>
@@ -2523,7 +2899,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>42</v>
@@ -2535,7 +2911,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
         <v>0.395420724337231</v>
@@ -2543,29 +2919,47 @@
       <c r="I11" t="n">
         <v>0.796428571428571</v>
       </c>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
+      <c r="J11" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.173624781822918</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.150327693860948</v>
+      </c>
       <c r="N11" t="n">
         <v>0.395420724337231</v>
       </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
+      <c r="O11" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.173624781822918</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.150327693860948</v>
+      </c>
       <c r="R11" t="n">
         <v>42</v>
       </c>
-      <c r="S11"/>
-      <c r="T11"/>
+      <c r="S11" t="n">
+        <v>-0.386875093221916</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.00285242014711681</v>
+      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X11" t="s">
         <v>44</v>
@@ -2576,10 +2970,10 @@
         <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>30</v>
@@ -2591,7 +2985,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>0.392983399454889</v>
@@ -2599,32 +2993,50 @@
       <c r="I12" t="n">
         <v>0.56043956043956</v>
       </c>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
+      <c r="J12" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.054726368159204</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.07563199840268</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.875160051717567</v>
+      </c>
       <c r="N12" t="n">
         <v>0.392983399454889</v>
       </c>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
+      <c r="O12" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.07563199840268</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.875160051717567</v>
+      </c>
       <c r="R12" t="n">
         <v>42</v>
       </c>
-      <c r="S12"/>
-      <c r="T12"/>
+      <c r="S12" t="n">
+        <v>-2.44133225480704</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.157076548920688</v>
+      </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="X12" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -2635,7 +3047,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -2647,7 +3059,7 @@
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
         <v>0.37156217891133</v>
@@ -2655,32 +3067,50 @@
       <c r="I13" t="n">
         <v>0.767032967032967</v>
       </c>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
+      <c r="J13" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.225358543648482</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.176778018485117</v>
+      </c>
       <c r="N13" t="n">
         <v>0.37156217891133</v>
       </c>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
+      <c r="O13" t="n">
+        <v>0.00497512437810945</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.225358543648482</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.176778018485117</v>
+      </c>
       <c r="R13" t="n">
         <v>42</v>
       </c>
-      <c r="S13"/>
-      <c r="T13"/>
+      <c r="S13" t="n">
+        <v>-0.524493540079265</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.072643159223403</v>
+      </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="X13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2688,10 +3118,10 @@
         <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
@@ -2703,7 +3133,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H14" t="n">
         <v>0.140992211958394</v>
@@ -2711,43 +3141,61 @@
       <c r="I14" t="n">
         <v>0.910714285714286</v>
       </c>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
+      <c r="J14" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-93.540728185107</v>
+      </c>
+      <c r="M14" t="n">
+        <v>104.537681598421</v>
+      </c>
       <c r="N14" t="n">
         <v>0.140992211958394</v>
       </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
+      <c r="O14" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-93.540728185107</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>104.537681598421</v>
+      </c>
       <c r="R14" t="n">
         <v>36</v>
       </c>
-      <c r="S14"/>
-      <c r="T14"/>
+      <c r="S14" t="n">
+        <v>-268.301815756177</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.6774278902307</v>
+      </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="X14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -2759,7 +3207,7 @@
         <v>1898</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" t="n">
         <v>0.457722008481763</v>
@@ -2767,43 +3215,61 @@
       <c r="I15" t="n">
         <v>0.698929220664338</v>
       </c>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
+      <c r="J15" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.728741920372084</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.667080858461555</v>
+      </c>
       <c r="N15" t="n">
         <v>0.457722008481763</v>
       </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
+      <c r="O15" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.728741920372084</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.667080858461555</v>
+      </c>
       <c r="R15" t="n">
         <v>42</v>
       </c>
-      <c r="S15"/>
-      <c r="T15"/>
+      <c r="S15" t="n">
+        <v>-1.82463181426028</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.30510650070914</v>
+      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>30</v>
@@ -2815,7 +3281,7 @@
         <v>1899</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H16" t="n">
         <v>0.355394439064757</v>
@@ -2823,43 +3289,61 @@
       <c r="I16" t="n">
         <v>0.564285714285714</v>
       </c>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
+      <c r="J16" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0298507462686567</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.354732305755251</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.325815812872284</v>
+      </c>
       <c r="N16" t="n">
         <v>0.355394439064757</v>
       </c>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
+      <c r="O16" t="n">
+        <v>0.0248756218905473</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.354732305755251</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.325815812872284</v>
+      </c>
       <c r="R16" t="n">
         <v>42</v>
       </c>
-      <c r="S16"/>
-      <c r="T16"/>
+      <c r="S16" t="n">
+        <v>-0.849998638044073</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.150065426610544</v>
+      </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -2871,7 +3355,7 @@
         <v>1899</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H17" t="n">
         <v>0.0866834108093932</v>
@@ -2879,43 +3363,61 @@
       <c r="I17" t="n">
         <v>0.292857142857143</v>
       </c>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
+      <c r="J17" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0497512437810945</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.170939231628711</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.128940063668492</v>
+      </c>
       <c r="N17" t="n">
         <v>0.0866834108093932</v>
       </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
+      <c r="O17" t="n">
+        <v>0.0348258706467662</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.170939231628711</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.128940063668492</v>
+      </c>
       <c r="R17" t="n">
         <v>42</v>
       </c>
-      <c r="S17"/>
-      <c r="T17"/>
+      <c r="S17" t="n">
+        <v>-0.366143996644589</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.043195208363013</v>
+      </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="X17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
@@ -2927,7 +3429,7 @@
         <v>1899</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H18" t="n">
         <v>0.0365935847765777</v>
@@ -2935,43 +3437,61 @@
       <c r="I18" t="n">
         <v>0.0428571428571429</v>
       </c>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
+      <c r="J18" t="n">
+        <v>0.0398009950248756</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0398009950248756</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.150062832444744</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0916940773108943</v>
+      </c>
       <c r="N18" t="n">
         <v>0.0365935847765777</v>
       </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
+      <c r="O18" t="n">
+        <v>0.0398009950248756</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.150062832444744</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.0916940773108943</v>
+      </c>
       <c r="R18" t="n">
         <v>42</v>
       </c>
-      <c r="S18"/>
-      <c r="T18"/>
+      <c r="S18" t="n">
+        <v>-0.250226196917061</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.0440590134715418</v>
+      </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="X18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
@@ -2983,7 +3503,7 @@
         <v>1898</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
         <v>-0.0210078015160711</v>
@@ -2991,21 +3511,39 @@
       <c r="I19" t="n">
         <v>-0.121973535668848</v>
       </c>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
+      <c r="J19" t="n">
+        <v>0.0895522388059701</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.109452736318408</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.17561000952502</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.145788357211688</v>
+      </c>
       <c r="N19" t="n">
         <v>-0.0210078015160711</v>
       </c>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19"/>
+      <c r="O19" t="n">
+        <v>0.0895522388059701</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.17561000952502</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.145788357211688</v>
+      </c>
       <c r="R19" t="n">
         <v>42</v>
       </c>
-      <c r="S19"/>
-      <c r="T19"/>
+      <c r="S19" t="n">
+        <v>-0.393686497706517</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.0752378579364235</v>
+      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -3013,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="X19" t="s">
         <v>38</v>
@@ -3021,13 +3559,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
@@ -3039,7 +3577,7 @@
         <v>5696</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
         <v>-0.0256414156241849</v>
@@ -3047,21 +3585,39 @@
       <c r="I20" t="n">
         <v>-0.107692307692308</v>
       </c>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
+      <c r="J20" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.160664435323007</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0235080662093789</v>
+      </c>
       <c r="N20" t="n">
         <v>-0.0256414156241849</v>
       </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
+      <c r="O20" t="n">
+        <v>0.0099502487562189</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.160664435323007</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0235080662093789</v>
+      </c>
       <c r="R20" t="n">
         <v>42</v>
       </c>
-      <c r="S20"/>
-      <c r="T20"/>
+      <c r="S20" t="n">
+        <v>-0.184320257891312</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.159763313609467</v>
+      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -3069,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="X20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3088,24 +3644,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" t="s">
         <v>110</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>111</v>
-      </c>
-      <c r="C1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B2" t="n">
         <v>0.24634128468443</v>
@@ -3114,15 +3670,15 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" t="n">
         <v>0.595923521891115</v>
@@ -3131,15 +3687,15 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B4" t="n">
         <v>0.0714725596606504</v>
@@ -3148,15 +3704,15 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" t="n">
         <v>0.106296359589286</v>
@@ -3165,15 +3721,15 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B6" t="n">
         <v>0.996331871821693</v>
@@ -3182,15 +3738,15 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" t="n">
         <v>0.70749566734604</v>
@@ -3199,15 +3755,15 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B8" t="n">
         <v>0.452009408018053</v>
@@ -3216,15 +3772,15 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B9" t="n">
         <v>0.93828696756471</v>
@@ -3233,15 +3789,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B10" t="n">
         <v>0.790766933331937</v>
@@ -3250,15 +3806,15 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" t="n">
         <v>0.860463045375293</v>
@@ -3270,12 +3826,12 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B12" t="n">
         <v>0.976623637038833</v>
@@ -3287,12 +3843,12 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B13" t="n">
         <v>0.0372181644372705</v>
@@ -3304,12 +3860,12 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B14" t="n">
         <v>0.00111117207844174</v>
@@ -3321,12 +3877,12 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B15" t="n">
         <v>0.925486027942554</v>
@@ -3338,12 +3894,12 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B16" t="n">
         <v>0.96180441127636</v>
@@ -3355,12 +3911,12 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B17" t="n">
         <v>0.133517708139971</v>
@@ -3372,12 +3928,12 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B18" t="n">
         <v>0.822899730107993</v>
@@ -3389,12 +3945,12 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B19" t="n">
         <v>0.0425029672208257</v>
@@ -3406,12 +3962,12 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B20" t="n">
         <v>0.241186637828355</v>
@@ -3423,12 +3979,12 @@
         <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B21" t="n">
         <v>0.941846637807116</v>
@@ -3440,12 +3996,12 @@
         <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B22" t="n">
         <v>0.0823720753199149</v>
@@ -3457,12 +4013,12 @@
         <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B23" t="n">
         <v>0.527193126890309</v>
@@ -3474,12 +4030,12 @@
         <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B24" t="n">
         <v>0.922584841692793</v>
@@ -3491,12 +4047,12 @@
         <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B25" t="n">
         <v>0.876530916682701</v>
@@ -3508,12 +4064,12 @@
         <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B26" t="n">
         <v>0.384311055119259</v>
@@ -3525,12 +4081,12 @@
         <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B27" t="n">
         <v>0.708162829885467</v>
@@ -3542,12 +4098,12 @@
         <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B28" t="n">
         <v>0.418656058555944</v>
@@ -3559,7 +4115,7 @@
         <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
